--- a/results/reports/summary_report.xlsx
+++ b/results/reports/summary_report.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,35 +471,45 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>top_30_return</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>top_30_excess</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>decile_return</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>decile_excess</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>decile_size_avg</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>OMXS30</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>OMXC25</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>OMXH25</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>OSEBX</t>
         </is>
@@ -528,18 +538,24 @@
         <v>32.22</v>
       </c>
       <c r="H2" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="I2" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="J2" t="n">
         <v>24.42</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>20.55</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>59</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -564,18 +580,24 @@
         <v>18.56</v>
       </c>
       <c r="H3" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="J3" t="n">
         <v>16.94</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>16.12</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>61</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -600,24 +622,30 @@
         <v>49.77</v>
       </c>
       <c r="H4" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="I4" t="n">
+        <v>43.59</v>
+      </c>
+      <c r="J4" t="n">
         <v>41.19</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>41.91</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>71</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>10.35</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>16.32</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>13</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>13.46</v>
       </c>
     </row>
@@ -644,24 +672,30 @@
         <v>40.36</v>
       </c>
       <c r="H5" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="I5" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="J5" t="n">
         <v>12.24</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>34.32</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>79</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>-15.55</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>-13.49</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>-13.4</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>-1.03</v>
       </c>
     </row>
@@ -688,24 +722,30 @@
         <v>69.91</v>
       </c>
       <c r="H6" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="I6" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="J6" t="n">
         <v>20.55</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>33.03</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>83</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>17.26</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>7.09</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>-6.41</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>9.890000000000001</v>
       </c>
     </row>
@@ -732,24 +772,30 @@
         <v>39.43</v>
       </c>
       <c r="H7" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="I7" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="J7" t="n">
         <v>32.66</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>36.56</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>84</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>3.63</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>-2.43</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>-4.43</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>9.06</v>
       </c>
     </row>
@@ -776,24 +822,30 @@
         <v>59.4</v>
       </c>
       <c r="H8" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="I8" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="J8" t="n">
         <v>42.79</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>48.48</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>86</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>16.1</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>2.66</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>32.15</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>18.44</v>
       </c>
     </row>
@@ -820,24 +872,30 @@
         <v>4.16</v>
       </c>
       <c r="H9" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="J9" t="n">
         <v>1.68</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>3.52</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>88</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>4.98</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>4.41</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>1.73</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>4.3</v>
       </c>
     </row>
@@ -852,7 +910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,25 +931,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>top_30_cumulative</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>decile_cumulative</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>OMXS30_cumulative</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>OMXC25_cumulative</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>OMXH25_cumulative</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>OSEBX_cumulative</t>
         </is>
@@ -908,10 +971,10 @@
         <v>136.09</v>
       </c>
       <c r="D2" t="n">
+        <v>130.12</v>
+      </c>
+      <c r="E2" t="n">
         <v>124.42</v>
-      </c>
-      <c r="E2" t="n">
-        <v>100</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -920,6 +983,9 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2" t="n">
         <v>100</v>
       </c>
     </row>
@@ -934,10 +1000,10 @@
         <v>162.46</v>
       </c>
       <c r="D3" t="n">
+        <v>142.81</v>
+      </c>
+      <c r="E3" t="n">
         <v>145.49</v>
-      </c>
-      <c r="E3" t="n">
-        <v>100</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -946,6 +1012,9 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I3" t="n">
         <v>100</v>
       </c>
     </row>
@@ -960,18 +1029,21 @@
         <v>242.13</v>
       </c>
       <c r="D4" t="n">
+        <v>204.03</v>
+      </c>
+      <c r="E4" t="n">
         <v>205.42</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>110.35</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>116.32</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>113</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>113.46</v>
       </c>
     </row>
@@ -986,18 +1058,21 @@
         <v>286.38</v>
       </c>
       <c r="D5" t="n">
+        <v>237.73</v>
+      </c>
+      <c r="E5" t="n">
         <v>230.57</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>93.18000000000001</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>100.64</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>97.86</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>112.29</v>
       </c>
     </row>
@@ -1012,18 +1087,21 @@
         <v>450.86</v>
       </c>
       <c r="D6" t="n">
+        <v>337.28</v>
+      </c>
+      <c r="E6" t="n">
         <v>277.96</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>109.27</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>107.78</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>91.58</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>123.4</v>
       </c>
     </row>
@@ -1038,18 +1116,21 @@
         <v>611.09</v>
       </c>
       <c r="D7" t="n">
+        <v>492.92</v>
+      </c>
+      <c r="E7" t="n">
         <v>368.74</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>113.24</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>105.16</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>87.53</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>134.58</v>
       </c>
     </row>
@@ -1064,18 +1145,21 @@
         <v>939.3</v>
       </c>
       <c r="D8" t="n">
+        <v>771.8099999999999</v>
+      </c>
+      <c r="E8" t="n">
         <v>526.53</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>131.47</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>107.95</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>115.67</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>159.4</v>
       </c>
     </row>
@@ -1090,18 +1174,21 @@
         <v>961.13</v>
       </c>
       <c r="D9" t="n">
+        <v>810.47</v>
+      </c>
+      <c r="E9" t="n">
         <v>535.39</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>138.02</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>112.71</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>117.67</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>166.25</v>
       </c>
     </row>
@@ -1116,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1152,25 +1239,30 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>top_30</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>decile</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>OMXS30</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>OMXC25</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>OMXH25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>OSEBX</t>
         </is>
@@ -1196,12 +1288,15 @@
         <v>3.22</v>
       </c>
       <c r="G2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H2" t="n">
         <v>-0.87</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1223,12 +1318,15 @@
         <v>2.26</v>
       </c>
       <c r="G3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H3" t="n">
         <v>2.53</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1250,12 +1348,15 @@
         <v>4.93</v>
       </c>
       <c r="G4" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="H4" t="n">
         <v>2.68</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1277,12 +1378,15 @@
         <v>5.8</v>
       </c>
       <c r="G5" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="H5" t="n">
         <v>2.12</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1304,12 +1408,15 @@
         <v>2.06</v>
       </c>
       <c r="G6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H6" t="n">
         <v>2.34</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,12 +1438,15 @@
         <v>1.11</v>
       </c>
       <c r="G7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H7" t="n">
         <v>2.18</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,12 +1468,15 @@
         <v>4.97</v>
       </c>
       <c r="G8" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="H8" t="n">
         <v>5.32</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1385,12 +1498,15 @@
         <v>3.53</v>
       </c>
       <c r="G9" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="H9" t="n">
         <v>2.88</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1412,12 +1528,15 @@
         <v>3.55</v>
       </c>
       <c r="G10" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="H10" t="n">
         <v>3.02</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1439,12 +1558,15 @@
         <v>-6.16</v>
       </c>
       <c r="G11" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H11" t="n">
         <v>-5.83</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1466,12 +1588,15 @@
         <v>-15.27</v>
       </c>
       <c r="G12" t="n">
+        <v>-17.15</v>
+      </c>
+      <c r="H12" t="n">
         <v>-15.96</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1493,12 +1618,15 @@
         <v>9.970000000000001</v>
       </c>
       <c r="G13" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H13" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1520,12 +1648,15 @@
         <v>3.12</v>
       </c>
       <c r="G14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H14" t="n">
         <v>5.58</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1547,12 +1678,15 @@
         <v>2.02</v>
       </c>
       <c r="G15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H15" t="n">
         <v>1.79</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1574,12 +1708,15 @@
         <v>2.73</v>
       </c>
       <c r="G16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H16" t="n">
         <v>3.97</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1601,12 +1738,15 @@
         <v>4.93</v>
       </c>
       <c r="G17" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="H17" t="n">
         <v>4.6</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1628,12 +1768,15 @@
         <v>4.13</v>
       </c>
       <c r="G18" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="H18" t="n">
         <v>4.12</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1655,12 +1798,15 @@
         <v>0.04</v>
       </c>
       <c r="G19" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="H19" t="n">
         <v>-3.57</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1682,12 +1828,15 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G20" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="H20" t="n">
         <v>8.01</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1709,12 +1858,15 @@
         <v>6.38</v>
       </c>
       <c r="G21" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="H21" t="n">
         <v>5.71</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1736,12 +1888,15 @@
         <v>0.33</v>
       </c>
       <c r="G22" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H22" t="n">
         <v>0.78</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1763,12 +1918,15 @@
         <v>8.27</v>
       </c>
       <c r="G23" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="H23" t="n">
         <v>6.06</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1790,12 +1948,15 @@
         <v>1.2</v>
       </c>
       <c r="G24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H24" t="n">
         <v>4.18</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1817,12 +1978,15 @@
         <v>6.65</v>
       </c>
       <c r="G25" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="H25" t="n">
         <v>6.42</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1844,18 +2008,21 @@
         <v>4.46</v>
       </c>
       <c r="G26" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H26" t="n">
         <v>2.96</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>1.1</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>4.53</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>3.83</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>1.66</v>
       </c>
     </row>
@@ -1879,18 +2046,21 @@
         <v>2.74</v>
       </c>
       <c r="G27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H27" t="n">
         <v>2.31</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>1.12</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>1.51</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>0.75</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2.8</v>
       </c>
     </row>
@@ -1914,18 +2084,21 @@
         <v>8.01</v>
       </c>
       <c r="G28" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="H28" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>0.95</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>3.76</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>3.37</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -1949,18 +2122,21 @@
         <v>2.51</v>
       </c>
       <c r="G29" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="H29" t="n">
         <v>1.71</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>4.72</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>3.5</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>5.52</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>1.19</v>
       </c>
     </row>
@@ -1984,18 +2160,21 @@
         <v>-3.36</v>
       </c>
       <c r="G30" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="H30" t="n">
         <v>-3.64</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>-0.79</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>2.58</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>0.78</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>0.67</v>
       </c>
     </row>
@@ -2019,18 +2198,21 @@
         <v>5.95</v>
       </c>
       <c r="G31" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="H31" t="n">
         <v>6.28</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>-3.92</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>-4.79</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>-5.66</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>1.88</v>
       </c>
     </row>
@@ -2054,18 +2236,21 @@
         <v>3.12</v>
       </c>
       <c r="G32" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H32" t="n">
         <v>1.26</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>1.4</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>4.82</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>0.74</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>2.53</v>
       </c>
     </row>
@@ -2089,18 +2274,21 @@
         <v>1.96</v>
       </c>
       <c r="G33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H33" t="n">
         <v>2.81</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>-2.15</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>-4.5</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>-1.62</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>-0.96</v>
       </c>
     </row>
@@ -2124,18 +2312,21 @@
         <v>-0.28</v>
       </c>
       <c r="G34" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="H34" t="n">
         <v>-2.7</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>7.94</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>4.41</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>5.11</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>1.71</v>
       </c>
     </row>
@@ -2159,18 +2350,21 @@
         <v>-3.13</v>
       </c>
       <c r="G35" t="n">
+        <v>-3.43</v>
+      </c>
+      <c r="H35" t="n">
         <v>-3.95</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>-5.35</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>-9.640000000000001</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>-4.85</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>-2.21</v>
       </c>
     </row>
@@ -2194,18 +2388,21 @@
         <v>4.97</v>
       </c>
       <c r="G36" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="H36" t="n">
         <v>3.61</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>-6.82</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>-0.64</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>-7.73</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>2.32</v>
       </c>
     </row>
@@ -2229,18 +2426,21 @@
         <v>-0.15</v>
       </c>
       <c r="G37" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H37" t="n">
         <v>-0.27</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>-1.82</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>1.21</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>-0.54</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>4.92</v>
       </c>
     </row>
@@ -2264,18 +2464,21 @@
         <v>-2.7</v>
       </c>
       <c r="G38" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="H38" t="n">
         <v>-1.95</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>-1.73</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>-1.2</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>0.36</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>-1.71</v>
       </c>
     </row>
@@ -2299,18 +2502,21 @@
         <v>-5.46</v>
       </c>
       <c r="G39" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="H39" t="n">
         <v>-5.89</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>-0.79</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>-4.67</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>-0.48</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>3.84</v>
       </c>
     </row>
@@ -2334,18 +2540,21 @@
         <v>3.6</v>
       </c>
       <c r="G40" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="H40" t="n">
         <v>6.6</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>-8.32</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>-6.39</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>-7.5</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>-9.1</v>
       </c>
     </row>
@@ -2369,18 +2578,21 @@
         <v>0.31</v>
       </c>
       <c r="G41" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H41" t="n">
         <v>-2.35</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>8.539999999999999</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>12.44</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>6.69</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>7.08</v>
       </c>
     </row>
@@ -2404,18 +2616,21 @@
         <v>-6.35</v>
       </c>
       <c r="G42" t="n">
+        <v>-4.06</v>
+      </c>
+      <c r="H42" t="n">
         <v>-5.41</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>-5.53</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>-6.66</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>-1.95</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>-0.36</v>
       </c>
     </row>
@@ -2439,18 +2654,21 @@
         <v>3.26</v>
       </c>
       <c r="G43" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="H43" t="n">
         <v>5.19</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>-4.75</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>-12.92</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>-6.8</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>-11.68</v>
       </c>
     </row>
@@ -2474,18 +2692,21 @@
         <v>7.46</v>
       </c>
       <c r="G44" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="H44" t="n">
         <v>8.34</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>7.63</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>9.42</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>5.11</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>6.59</v>
       </c>
     </row>
@@ -2509,18 +2730,21 @@
         <v>4.05</v>
       </c>
       <c r="G45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H45" t="n">
         <v>1.24</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>6.8</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>7.11</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>6.93</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>3.85</v>
       </c>
     </row>
@@ -2544,18 +2768,21 @@
         <v>12.7</v>
       </c>
       <c r="G46" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="H46" t="n">
         <v>7.88</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>-2.81</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>0.83</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>-2.03</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>-2.6</v>
       </c>
     </row>
@@ -2579,18 +2806,21 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G47" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="H47" t="n">
         <v>3.37</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>7.59</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>-0.13</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>2.34</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>0.54</v>
       </c>
     </row>
@@ -2614,18 +2844,21 @@
         <v>1.68</v>
       </c>
       <c r="G48" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H48" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>1.28</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>4.82</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>1.79</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -2649,18 +2882,21 @@
         <v>2.8</v>
       </c>
       <c r="G49" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="H49" t="n">
         <v>1.78</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>-0.14</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>0.55</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>-4.96</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>-3.82</v>
       </c>
     </row>
@@ -2684,18 +2920,21 @@
         <v>-0.24</v>
       </c>
       <c r="G50" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="H50" t="n">
         <v>-2.77</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>2.11</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>1.58</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>-0.58</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -2719,18 +2958,21 @@
         <v>5.96</v>
       </c>
       <c r="G51" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="H51" t="n">
         <v>2.92</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>-1.57</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>-0.87</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>-6.04</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>-2.27</v>
       </c>
     </row>
@@ -2754,18 +2996,21 @@
         <v>1.24</v>
       </c>
       <c r="G52" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H52" t="n">
         <v>1.61</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>3.35</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>0.78</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>-0.97</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -2789,18 +3034,21 @@
         <v>2.66</v>
       </c>
       <c r="G53" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="H53" t="n">
         <v>-0.25</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>-2.55</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>-0.39</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>-0.72</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>2.54</v>
       </c>
     </row>
@@ -2824,18 +3072,21 @@
         <v>1.85</v>
       </c>
       <c r="G54" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H54" t="n">
         <v>1.49</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>-2.94</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>-4.05</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>-0.21</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>0.86</v>
       </c>
     </row>
@@ -2859,18 +3110,21 @@
         <v>-0.11</v>
       </c>
       <c r="G55" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="H55" t="n">
         <v>-0.96</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>-1.34</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>-2.06</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>-2.5</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>2.82</v>
       </c>
     </row>
@@ -2894,18 +3148,21 @@
         <v>3.75</v>
       </c>
       <c r="G56" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="H56" t="n">
         <v>4.81</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>-3.7</v>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
         <v>-4.74</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>-3.53</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>-0.77</v>
       </c>
     </row>
@@ -2929,18 +3186,21 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G57" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="H57" t="n">
         <v>5.25</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>7.55</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>6.69</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>6.31</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>1.78</v>
       </c>
     </row>
@@ -2964,18 +3224,21 @@
         <v>8.99</v>
       </c>
       <c r="G58" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="H58" t="n">
         <v>3.33</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>7.33</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>5.37</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>3.13</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -2999,18 +3262,21 @@
         <v>4.25</v>
       </c>
       <c r="G59" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="H59" t="n">
         <v>1.97</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>-1.65</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>1.94</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>0.73</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>-2.17</v>
       </c>
     </row>
@@ -3034,18 +3300,21 @@
         <v>2.65</v>
       </c>
       <c r="G60" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="H60" t="n">
         <v>4.34</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>4.08</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>2.18</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>-2.76</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>-0.96</v>
       </c>
     </row>
@@ -3069,18 +3338,21 @@
         <v>-0.18</v>
       </c>
       <c r="G61" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H61" t="n">
         <v>0.97</v>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>2.67</v>
       </c>
-      <c r="I61" t="n">
+      <c r="J61" t="n">
         <v>2.44</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>-0.77</v>
       </c>
-      <c r="K61" t="n">
+      <c r="L61" t="n">
         <v>4.9</v>
       </c>
     </row>
@@ -3104,18 +3376,21 @@
         <v>2.46</v>
       </c>
       <c r="G62" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H62" t="n">
         <v>3.78</v>
       </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>1.51</v>
       </c>
-      <c r="I62" t="n">
+      <c r="J62" t="n">
         <v>-1.97</v>
       </c>
-      <c r="J62" t="n">
+      <c r="K62" t="n">
         <v>1.52</v>
       </c>
-      <c r="K62" t="n">
+      <c r="L62" t="n">
         <v>3.24</v>
       </c>
     </row>
@@ -3139,18 +3414,21 @@
         <v>0.04</v>
       </c>
       <c r="G63" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H63" t="n">
         <v>-0.08</v>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>1.87</v>
       </c>
-      <c r="I63" t="n">
+      <c r="J63" t="n">
         <v>4.05</v>
       </c>
-      <c r="J63" t="n">
+      <c r="K63" t="n">
         <v>3.84</v>
       </c>
-      <c r="K63" t="n">
+      <c r="L63" t="n">
         <v>5.06</v>
       </c>
     </row>
@@ -3174,18 +3452,21 @@
         <v>3.19</v>
       </c>
       <c r="G64" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H64" t="n">
         <v>2.29</v>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>-1.33</v>
       </c>
-      <c r="I64" t="n">
+      <c r="J64" t="n">
         <v>-1.45</v>
       </c>
-      <c r="J64" t="n">
+      <c r="K64" t="n">
         <v>-2.93</v>
       </c>
-      <c r="K64" t="n">
+      <c r="L64" t="n">
         <v>-1.26</v>
       </c>
     </row>
@@ -3209,18 +3490,21 @@
         <v>2.96</v>
       </c>
       <c r="G65" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H65" t="n">
         <v>1.08</v>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
         <v>1.55</v>
       </c>
-      <c r="I65" t="n">
+      <c r="J65" t="n">
         <v>2.93</v>
       </c>
-      <c r="J65" t="n">
+      <c r="K65" t="n">
         <v>1.03</v>
       </c>
-      <c r="K65" t="n">
+      <c r="L65" t="n">
         <v>2.6</v>
       </c>
     </row>
@@ -3244,18 +3528,21 @@
         <v>3.08</v>
       </c>
       <c r="G66" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="H66" t="n">
         <v>2.27</v>
       </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
         <v>-0.51</v>
       </c>
-      <c r="I66" t="n">
+      <c r="J66" t="n">
         <v>-1.06</v>
       </c>
-      <c r="J66" t="n">
+      <c r="K66" t="n">
         <v>3.14</v>
       </c>
-      <c r="K66" t="n">
+      <c r="L66" t="n">
         <v>-1.36</v>
       </c>
     </row>
@@ -3279,18 +3566,21 @@
         <v>2.6</v>
       </c>
       <c r="G67" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H67" t="n">
         <v>2.29</v>
       </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
         <v>1.17</v>
       </c>
-      <c r="I67" t="n">
+      <c r="J67" t="n">
         <v>-1.98</v>
       </c>
-      <c r="J67" t="n">
+      <c r="K67" t="n">
         <v>1.2</v>
       </c>
-      <c r="K67" t="n">
+      <c r="L67" t="n">
         <v>-1.61</v>
       </c>
     </row>
@@ -3314,18 +3604,21 @@
         <v>1.9</v>
       </c>
       <c r="G68" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H68" t="n">
         <v>0.4</v>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
         <v>-3.2</v>
       </c>
-      <c r="I68" t="n">
+      <c r="J68" t="n">
         <v>-3.8</v>
       </c>
-      <c r="J68" t="n">
+      <c r="K68" t="n">
         <v>-5.54</v>
       </c>
-      <c r="K68" t="n">
+      <c r="L68" t="n">
         <v>1.07</v>
       </c>
     </row>
@@ -3349,18 +3642,21 @@
         <v>2.06</v>
       </c>
       <c r="G69" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H69" t="n">
         <v>2.33</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
         <v>-1.12</v>
       </c>
-      <c r="I69" t="n">
+      <c r="J69" t="n">
         <v>-1.26</v>
       </c>
-      <c r="J69" t="n">
+      <c r="K69" t="n">
         <v>-3.1</v>
       </c>
-      <c r="K69" t="n">
+      <c r="L69" t="n">
         <v>1.59</v>
       </c>
     </row>
@@ -3384,18 +3680,21 @@
         <v>5.94</v>
       </c>
       <c r="G70" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="H70" t="n">
         <v>7.15</v>
       </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
         <v>-1.22</v>
       </c>
-      <c r="I70" t="n">
+      <c r="J70" t="n">
         <v>-4.06</v>
       </c>
-      <c r="J70" t="n">
+      <c r="K70" t="n">
         <v>-0.43</v>
       </c>
-      <c r="K70" t="n">
+      <c r="L70" t="n">
         <v>-2.01</v>
       </c>
     </row>
@@ -3419,18 +3718,21 @@
         <v>10.95</v>
       </c>
       <c r="G71" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="H71" t="n">
         <v>7.08</v>
       </c>
-      <c r="H71" t="n">
+      <c r="I71" t="n">
         <v>7.55</v>
       </c>
-      <c r="I71" t="n">
+      <c r="J71" t="n">
         <v>-0.21</v>
       </c>
-      <c r="J71" t="n">
+      <c r="K71" t="n">
         <v>5.9</v>
       </c>
-      <c r="K71" t="n">
+      <c r="L71" t="n">
         <v>6.34</v>
       </c>
     </row>
@@ -3454,18 +3756,21 @@
         <v>4.27</v>
       </c>
       <c r="G72" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="H72" t="n">
         <v>-0.26</v>
       </c>
-      <c r="H72" t="n">
+      <c r="I72" t="n">
         <v>2.03</v>
       </c>
-      <c r="I72" t="n">
+      <c r="J72" t="n">
         <v>4.41</v>
       </c>
-      <c r="J72" t="n">
+      <c r="K72" t="n">
         <v>3.26</v>
       </c>
-      <c r="K72" t="n">
+      <c r="L72" t="n">
         <v>-1.7</v>
       </c>
     </row>
@@ -3489,18 +3794,21 @@
         <v>3.31</v>
       </c>
       <c r="G73" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="H73" t="n">
         <v>1.65</v>
       </c>
-      <c r="H73" t="n">
+      <c r="I73" t="n">
         <v>-8.460000000000001</v>
       </c>
-      <c r="I73" t="n">
+      <c r="J73" t="n">
         <v>-9.949999999999999</v>
       </c>
-      <c r="J73" t="n">
+      <c r="K73" t="n">
         <v>-4.54</v>
       </c>
-      <c r="K73" t="n">
+      <c r="L73" t="n">
         <v>1.8</v>
       </c>
     </row>
@@ -3524,18 +3832,21 @@
         <v>2.55</v>
       </c>
       <c r="G74" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="H74" t="n">
         <v>3.54</v>
       </c>
-      <c r="H74" t="n">
+      <c r="I74" t="n">
         <v>-2.41</v>
       </c>
-      <c r="I74" t="n">
+      <c r="J74" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="J74" t="n">
+      <c r="K74" t="n">
         <v>-0.19</v>
       </c>
-      <c r="K74" t="n">
+      <c r="L74" t="n">
         <v>-1.94</v>
       </c>
     </row>
@@ -3559,18 +3870,21 @@
         <v>0.98</v>
       </c>
       <c r="G75" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H75" t="n">
         <v>1.23</v>
       </c>
-      <c r="H75" t="n">
+      <c r="I75" t="n">
         <v>2.55</v>
       </c>
-      <c r="I75" t="n">
+      <c r="J75" t="n">
         <v>6.37</v>
       </c>
-      <c r="J75" t="n">
+      <c r="K75" t="n">
         <v>5.2</v>
       </c>
-      <c r="K75" t="n">
+      <c r="L75" t="n">
         <v>5.01</v>
       </c>
     </row>
@@ -3594,18 +3908,21 @@
         <v>3.39</v>
       </c>
       <c r="G76" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H76" t="n">
         <v>3.42</v>
       </c>
-      <c r="H76" t="n">
+      <c r="I76" t="n">
         <v>-0.1</v>
       </c>
-      <c r="I76" t="n">
+      <c r="J76" t="n">
         <v>-3.12</v>
       </c>
-      <c r="J76" t="n">
+      <c r="K76" t="n">
         <v>1.06</v>
       </c>
-      <c r="K76" t="n">
+      <c r="L76" t="n">
         <v>3.82</v>
       </c>
     </row>
@@ -3629,18 +3946,21 @@
         <v>1.94</v>
       </c>
       <c r="G77" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="H77" t="n">
         <v>2.74</v>
       </c>
-      <c r="H77" t="n">
+      <c r="I77" t="n">
         <v>3.47</v>
       </c>
-      <c r="I77" t="n">
+      <c r="J77" t="n">
         <v>-2.42</v>
       </c>
-      <c r="J77" t="n">
+      <c r="K77" t="n">
         <v>1.6</v>
       </c>
-      <c r="K77" t="n">
+      <c r="L77" t="n">
         <v>0.24</v>
       </c>
     </row>
@@ -3664,18 +3984,21 @@
         <v>2.96</v>
       </c>
       <c r="G78" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H78" t="n">
         <v>1.39</v>
       </c>
-      <c r="H78" t="n">
+      <c r="I78" t="n">
         <v>1.77</v>
       </c>
-      <c r="I78" t="n">
+      <c r="J78" t="n">
         <v>0.09</v>
       </c>
-      <c r="J78" t="n">
+      <c r="K78" t="n">
         <v>1.36</v>
       </c>
-      <c r="K78" t="n">
+      <c r="L78" t="n">
         <v>1.31</v>
       </c>
     </row>
@@ -3699,18 +4022,21 @@
         <v>2.82</v>
       </c>
       <c r="G79" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H79" t="n">
         <v>3.11</v>
       </c>
-      <c r="H79" t="n">
+      <c r="I79" t="n">
         <v>1.41</v>
       </c>
-      <c r="I79" t="n">
+      <c r="J79" t="n">
         <v>-2.3</v>
       </c>
-      <c r="J79" t="n">
+      <c r="K79" t="n">
         <v>1.89</v>
       </c>
-      <c r="K79" t="n">
+      <c r="L79" t="n">
         <v>-0.12</v>
       </c>
     </row>
@@ -3734,18 +4060,21 @@
         <v>2.03</v>
       </c>
       <c r="G80" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="H80" t="n">
         <v>2.85</v>
       </c>
-      <c r="H80" t="n">
+      <c r="I80" t="n">
         <v>3.92</v>
       </c>
-      <c r="I80" t="n">
+      <c r="J80" t="n">
         <v>3.48</v>
       </c>
-      <c r="J80" t="n">
+      <c r="K80" t="n">
         <v>9.27</v>
       </c>
-      <c r="K80" t="n">
+      <c r="L80" t="n">
         <v>-1.99</v>
       </c>
     </row>
@@ -3769,18 +4098,21 @@
         <v>5.49</v>
       </c>
       <c r="G81" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="H81" t="n">
         <v>4.92</v>
       </c>
-      <c r="H81" t="n">
+      <c r="I81" t="n">
         <v>0.75</v>
       </c>
-      <c r="I81" t="n">
+      <c r="J81" t="n">
         <v>3.66</v>
       </c>
-      <c r="J81" t="n">
+      <c r="K81" t="n">
         <v>-0.92</v>
       </c>
-      <c r="K81" t="n">
+      <c r="L81" t="n">
         <v>-0.13</v>
       </c>
     </row>
@@ -3804,18 +4136,21 @@
         <v>3.41</v>
       </c>
       <c r="G82" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="H82" t="n">
         <v>4.7</v>
       </c>
-      <c r="H82" t="n">
+      <c r="I82" t="n">
         <v>3.41</v>
       </c>
-      <c r="I82" t="n">
+      <c r="J82" t="n">
         <v>4.44</v>
       </c>
-      <c r="J82" t="n">
+      <c r="K82" t="n">
         <v>5.03</v>
       </c>
-      <c r="K82" t="n">
+      <c r="L82" t="n">
         <v>4.85</v>
       </c>
     </row>
@@ -3839,18 +4174,21 @@
         <v>2.32</v>
       </c>
       <c r="G83" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="H83" t="n">
         <v>1.68</v>
       </c>
-      <c r="H83" t="n">
+      <c r="I83" t="n">
         <v>4.98</v>
       </c>
-      <c r="I83" t="n">
+      <c r="J83" t="n">
         <v>4.41</v>
       </c>
-      <c r="J83" t="n">
+      <c r="K83" t="n">
         <v>1.73</v>
       </c>
-      <c r="K83" t="n">
+      <c r="L83" t="n">
         <v>4.3</v>
       </c>
     </row>
@@ -6621,7 +6959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6679,120 +7017,150 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Avg Decile Annual Return</t>
+          <t>Avg Top 30 Annual Return</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.06</v>
+        <v>31.11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Avg Benchmark Annual Return</t>
+          <t>Avg Top 30 Annual Excess</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-5.25</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Final Cumulative - Benchmark</t>
+          <t>Avg Decile Annual Return</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63.08</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Final Cumulative - Top 20</t>
+          <t>Avg Benchmark Annual Return</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>961.13</v>
+        <v>-5.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Final Cumulative - Decile</t>
+          <t>Final Cumulative - Benchmark</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>535.39</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Final Cumulative - OMXS30 (Sweden)</t>
+          <t>Final Cumulative - Top 20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>138.02</v>
+        <v>961.13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Final Cumulative - OMXC25 (Denmark)</t>
+          <t>Final Cumulative - Top 30</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>112.71</v>
+        <v>810.47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Final Cumulative - OMXH25 (Finland)</t>
+          <t>Final Cumulative - Decile</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>117.67</v>
+        <v>535.39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Final Cumulative - OSEBX (Norway)</t>
+          <t>Final Cumulative - OMXS30 (Sweden)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>166.25</v>
+        <v>138.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Years Outperformed (Top N vs Benchmark)</t>
+          <t>Final Cumulative - OMXC25 (Denmark)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>112.71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Total Test Years</t>
+          <t>Final Cumulative - OMXH25 (Finland)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>117.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Final Cumulative - OSEBX (Norway)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>166.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Years Outperformed (Top N vs Benchmark)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Total Test Years</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Total Test Months</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B20" t="n">
         <v>82</v>
       </c>
     </row>
@@ -6807,7 +7175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6833,30 +7201,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Top 30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Decile</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Beat? (vs OMXS30)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>OMXS30</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>OMXC25</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>OMXH25</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>OSEBX</t>
         </is>
@@ -6876,17 +7249,20 @@
         <v>36.09</v>
       </c>
       <c r="E2" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="F2" t="n">
         <v>24.42</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -6902,17 +7278,20 @@
         <v>19.37</v>
       </c>
       <c r="E3" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="F3" t="n">
         <v>16.94</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6928,23 +7307,26 @@
         <v>49.04</v>
       </c>
       <c r="E4" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="F4" t="n">
         <v>41.19</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>10.35</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>16.32</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>13</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>13.46</v>
       </c>
     </row>
@@ -6962,23 +7344,26 @@
         <v>18.28</v>
       </c>
       <c r="E5" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="F5" t="n">
         <v>12.24</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>-15.55</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>-13.49</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>-13.4</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>-1.03</v>
       </c>
     </row>
@@ -6996,23 +7381,26 @@
         <v>57.44</v>
       </c>
       <c r="E6" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="F6" t="n">
         <v>20.55</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>17.26</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>7.09</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>-6.41</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>9.890000000000001</v>
       </c>
     </row>
@@ -7030,23 +7418,26 @@
         <v>35.54</v>
       </c>
       <c r="E7" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="F7" t="n">
         <v>32.66</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>3.63</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>-2.43</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>-4.43</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>9.06</v>
       </c>
     </row>
@@ -7064,23 +7455,26 @@
         <v>53.71</v>
       </c>
       <c r="E8" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="F8" t="n">
         <v>42.79</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>16.1</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>2.66</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>32.15</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>18.44</v>
       </c>
     </row>
@@ -7098,23 +7492,26 @@
         <v>2.32</v>
       </c>
       <c r="E9" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="F9" t="n">
         <v>1.68</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>4.98</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>4.41</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1.73</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>4.3</v>
       </c>
     </row>

--- a/results/reports/summary_report.xlsx
+++ b/results/reports/summary_report.xlsx
@@ -637,16 +637,16 @@
         <v>71</v>
       </c>
       <c r="M4" t="n">
-        <v>10.35</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>16.32</v>
+        <v>11.28</v>
       </c>
       <c r="O4" t="n">
-        <v>13</v>
+        <v>8.83</v>
       </c>
       <c r="P4" t="n">
-        <v>13.46</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="5">
@@ -1035,16 +1035,16 @@
         <v>205.42</v>
       </c>
       <c r="F4" t="n">
-        <v>110.35</v>
+        <v>109.14</v>
       </c>
       <c r="G4" t="n">
-        <v>116.32</v>
+        <v>111.28</v>
       </c>
       <c r="H4" t="n">
-        <v>113</v>
+        <v>108.83</v>
       </c>
       <c r="I4" t="n">
-        <v>113.46</v>
+        <v>111.61</v>
       </c>
     </row>
     <row r="5">
@@ -1064,16 +1064,16 @@
         <v>230.57</v>
       </c>
       <c r="F5" t="n">
-        <v>93.18000000000001</v>
+        <v>92.17</v>
       </c>
       <c r="G5" t="n">
-        <v>100.64</v>
+        <v>96.27</v>
       </c>
       <c r="H5" t="n">
-        <v>97.86</v>
+        <v>94.25</v>
       </c>
       <c r="I5" t="n">
-        <v>112.29</v>
+        <v>110.46</v>
       </c>
     </row>
     <row r="6">
@@ -1093,16 +1093,16 @@
         <v>277.96</v>
       </c>
       <c r="F6" t="n">
-        <v>109.27</v>
+        <v>108.08</v>
       </c>
       <c r="G6" t="n">
-        <v>107.78</v>
+        <v>103.1</v>
       </c>
       <c r="H6" t="n">
-        <v>91.58</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>123.4</v>
+        <v>121.38</v>
       </c>
     </row>
     <row r="7">
@@ -1122,16 +1122,16 @@
         <v>368.74</v>
       </c>
       <c r="F7" t="n">
-        <v>113.24</v>
+        <v>112</v>
       </c>
       <c r="G7" t="n">
-        <v>105.16</v>
+        <v>100.6</v>
       </c>
       <c r="H7" t="n">
-        <v>87.53</v>
+        <v>84.3</v>
       </c>
       <c r="I7" t="n">
-        <v>134.58</v>
+        <v>132.38</v>
       </c>
     </row>
     <row r="8">
@@ -1151,16 +1151,16 @@
         <v>526.53</v>
       </c>
       <c r="F8" t="n">
-        <v>131.47</v>
+        <v>130.04</v>
       </c>
       <c r="G8" t="n">
-        <v>107.95</v>
+        <v>103.27</v>
       </c>
       <c r="H8" t="n">
-        <v>115.67</v>
+        <v>111.4</v>
       </c>
       <c r="I8" t="n">
-        <v>159.4</v>
+        <v>156.79</v>
       </c>
     </row>
     <row r="9">
@@ -1180,16 +1180,16 @@
         <v>535.39</v>
       </c>
       <c r="F9" t="n">
-        <v>138.02</v>
+        <v>136.52</v>
       </c>
       <c r="G9" t="n">
-        <v>112.71</v>
+        <v>107.83</v>
       </c>
       <c r="H9" t="n">
-        <v>117.67</v>
+        <v>113.33</v>
       </c>
       <c r="I9" t="n">
-        <v>166.25</v>
+        <v>163.54</v>
       </c>
     </row>
   </sheetData>
@@ -2013,18 +2013,10 @@
       <c r="H26" t="n">
         <v>2.96</v>
       </c>
-      <c r="I26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.66</v>
-      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -7101,7 +7093,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>138.02</v>
+        <v>136.52</v>
       </c>
     </row>
     <row r="15">
@@ -7111,7 +7103,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>112.71</v>
+        <v>107.83</v>
       </c>
     </row>
     <row r="16">
@@ -7121,7 +7113,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>117.67</v>
+        <v>113.33</v>
       </c>
     </row>
     <row r="17">
@@ -7131,7 +7123,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>166.25</v>
+        <v>163.54</v>
       </c>
     </row>
     <row r="18">
@@ -7318,16 +7310,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>10.35</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>16.32</v>
+        <v>11.28</v>
       </c>
       <c r="J4" t="n">
-        <v>13</v>
+        <v>8.83</v>
       </c>
       <c r="K4" t="n">
-        <v>13.46</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="5">
